--- a/selected-work/data/publications.xlsx
+++ b/selected-work/data/publications.xlsx
@@ -16,9 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
     <t xml:space="preserve">August 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">September 2026</t>
   </si>
 </sst>
 </file>
@@ -38,8 +41,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
       <b/>
     </font>
   </fonts>
@@ -2745,7 +2746,7 @@
         </is>
       </c>
       <c r="B3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -2766,10 +2767,8 @@
           <t>tail_count</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="B5" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -2778,10 +2777,8 @@
           <t>tail_total</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
+      <c r="B6" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="7">
